--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shuva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\100to1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF9106A-F46A-466E-A9B2-04CE7A472080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45561843-B8E1-400B-8888-372E7F498D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="192" windowWidth="15264" windowHeight="16272" firstSheet="4" activeTab="6" xr2:uid="{04EDCA32-3258-430A-9858-4E806ABD8038}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="2" activeTab="5" xr2:uid="{04EDCA32-3258-430A-9858-4E806ABD8038}"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Паприка</t>
   </si>
@@ -162,9 +162,6 @@
     <t>май тай</t>
   </si>
   <si>
-    <t>красное вино</t>
-  </si>
-  <si>
     <t>пиво</t>
   </si>
   <si>
@@ -190,6 +187,18 @@
   </si>
   <si>
     <t>виски jack daniels</t>
+  </si>
+  <si>
+    <t>Лосось и авокадо</t>
+  </si>
+  <si>
+    <t>филе о фиш</t>
+  </si>
+  <si>
+    <t>вино</t>
+  </si>
+  <si>
+    <t>сыр</t>
   </si>
 </sst>
 </file>
@@ -542,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C94310-6447-4FF4-A8F3-9130BD60F43C}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="1"/>
@@ -614,9 +623,25 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
     </row>
@@ -646,7 +671,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -664,7 +689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CB6518-FE90-42B3-A9DB-46F6B7967528}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
@@ -699,7 +724,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -715,6 +740,14 @@
         <v>16</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7">
         <v>1</v>
       </c>
     </row>
@@ -760,7 +793,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -797,7 +830,7 @@
         <v>23</v>
       </c>
       <c r="B1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -866,7 +899,7 @@
         <v>30</v>
       </c>
       <c r="B1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -943,7 +976,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -951,7 +984,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -996,15 +1029,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1012,7 +1045,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1020,7 +1053,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1028,7 +1061,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1036,7 +1069,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1044,7 +1077,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10">
         <v>1</v>

--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\100to1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\www\100to1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45561843-B8E1-400B-8888-372E7F498D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="2" activeTab="5" xr2:uid="{04EDCA32-3258-430A-9858-4E806ABD8038}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="Безалкогольный" sheetId="6" r:id="rId6"/>
     <sheet name="Алкогольный" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Паприка</t>
   </si>
@@ -198,13 +197,28 @@
     <t>вино</t>
   </si>
   <si>
-    <t>сыр</t>
+    <t>Сыр</t>
+  </si>
+  <si>
+    <t>Малосольный огурец</t>
+  </si>
+  <si>
+    <t>русская картошка</t>
+  </si>
+  <si>
+    <t>двойной чизбургер</t>
+  </si>
+  <si>
+    <t>облепиховый морс</t>
+  </si>
+  <si>
+    <t>кофейный стаут</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -550,11 +564,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C94310-6447-4FF4-A8F3-9130BD60F43C}">
-  <dimension ref="A1:B11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,6 +656,14 @@
         <v>55</v>
       </c>
       <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
     </row>
@@ -651,8 +673,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA880A9-4EC3-41FA-9781-BBA79677C3FF}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
@@ -682,14 +704,22 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29CB6518-FE90-42B3-A9DB-46F6B7967528}">
-  <dimension ref="A1:B7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
@@ -751,13 +781,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C254E522-5324-41A4-8082-16D34ACD709E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -818,7 +856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC4C94E-F50A-43F3-8F42-5FB3636576F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -830,7 +868,7 @@
         <v>23</v>
       </c>
       <c r="B1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -887,8 +925,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DDB95F-0E4A-4B37-8013-1C59246BE7C5}">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.109375" customWidth="1"/>
@@ -990,14 +1028,22 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC95523A-629D-4E9F-BFEC-A87A150147B8}">
-  <dimension ref="A1:B10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
@@ -1083,6 +1129,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Паприка</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>кофейный стаут</t>
+  </si>
+  <si>
+    <t>Лобстер</t>
+  </si>
+  <si>
+    <t>коктейль белый русский</t>
   </si>
 </sst>
 </file>
@@ -565,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" customWidth="1"/>
@@ -664,6 +670,14 @@
         <v>56</v>
       </c>
       <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -693,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -754,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -807,7 +821,7 @@
         <v>17</v>
       </c>
       <c r="B1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -868,7 +882,7 @@
         <v>23</v>
       </c>
       <c r="B1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -953,7 +967,7 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1043,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
@@ -1137,6 +1151,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Паприка</t>
-  </si>
-  <si>
-    <t>Острый сыр</t>
   </si>
   <si>
     <t>Грибы</t>
@@ -571,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" customWidth="1"/>
@@ -587,7 +584,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -606,7 +603,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -614,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -635,7 +632,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -643,7 +640,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -651,10 +648,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -667,17 +664,9 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -696,7 +685,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1">
         <v>6</v>
@@ -704,7 +693,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -712,7 +701,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -720,7 +709,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -741,7 +730,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1">
         <v>2</v>
@@ -749,7 +738,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -757,7 +746,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -765,7 +754,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -773,7 +762,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -781,7 +770,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -789,7 +778,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -797,7 +786,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -818,7 +807,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1">
         <v>3</v>
@@ -826,7 +815,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -834,7 +823,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -842,7 +831,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -850,7 +839,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -858,7 +847,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -879,7 +868,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1">
         <v>7</v>
@@ -887,7 +876,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -895,7 +884,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -903,7 +892,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -911,7 +900,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -919,7 +908,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -927,7 +916,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -948,7 +937,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1">
         <v>6</v>
@@ -956,7 +945,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -964,7 +953,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -972,7 +961,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -980,7 +969,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -988,7 +977,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -996,7 +985,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1004,7 +993,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1012,7 +1001,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1020,7 +1009,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1028,7 +1017,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1036,7 +1025,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1044,7 +1033,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1065,7 +1054,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1">
         <v>2</v>
@@ -1073,7 +1062,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1081,7 +1070,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1089,7 +1078,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -1097,7 +1086,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -1105,7 +1094,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1113,7 +1102,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1121,7 +1110,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1129,7 +1118,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1137,7 +1126,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1145,7 +1134,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1153,7 +1142,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <v>1</v>

--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\www\100to1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\100to1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E10280D-9871-4799-89F9-A80EF012F60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656"/>
+    <workbookView xWindow="16164" yWindow="0" windowWidth="14652" windowHeight="16656" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Паприка</t>
   </si>
@@ -216,12 +217,18 @@
   </si>
   <si>
     <t>коктейль белый русский</t>
+  </si>
+  <si>
+    <t>Sushistore</t>
+  </si>
+  <si>
+    <t>глинтвейн</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -567,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -676,7 +683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -696,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -721,7 +728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -733,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="B1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -798,8 +805,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -853,13 +860,21 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -871,7 +886,7 @@
         <v>22</v>
       </c>
       <c r="B1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -928,7 +943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -948,7 +963,7 @@
         <v>30</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1045,8 +1060,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
@@ -1148,6 +1163,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Любимый хавчик.xlsx
+++ b/Любимый хавчик.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\100to1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E10280D-9871-4799-89F9-A80EF012F60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEA6C42-7E08-472D-B4E8-7D141D0540FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16164" yWindow="0" windowWidth="14652" windowHeight="16656" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Вкус чипсов" sheetId="1" r:id="rId1"/>
@@ -658,7 +658,7 @@
         <v>54</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
